--- a/source/guides/cdc/opioid-cds/ValueSet-hospice-disposition.xlsx
+++ b/source/guides/cdc/opioid-cds/ValueSet-hospice-disposition.xlsx
@@ -7,13 +7,14 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Expansion" r:id="rId4" sheetId="2"/>
+    <sheet name="Expansion Parameters" r:id="rId4" sheetId="2"/>
+    <sheet name="Expansion" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="48">
   <si>
     <t>Property</t>
   </si>
@@ -27,10 +28,16 @@
     <t>http://fhir.org/guides/cdc/opioid-cds/ValueSet/hospice-disposition</t>
   </si>
   <si>
+    <t>Identifier</t>
+  </si>
+  <si>
+    <t>OID:2.16.840.1.114222.48.48</t>
+  </si>
+  <si>
     <t>Version</t>
   </si>
   <si>
-    <t>2022.1.0</t>
+    <t>2022.1.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -105,15 +112,24 @@
     <t>BooleanType[null]</t>
   </si>
   <si>
+    <t>Parameter</t>
+  </si>
+  <si>
+    <t>used-codesystem</t>
+  </si>
+  <si>
+    <t>http://snomed.info/sct|http://snomed.info/sct/731000124108/version/20250901</t>
+  </si>
+  <si>
+    <t>version</t>
+  </si>
+  <si>
     <t>Level</t>
   </si>
   <si>
     <t>System</t>
   </si>
   <si>
-    <t>version</t>
-  </si>
-  <si>
     <t>Code</t>
   </si>
   <si>
@@ -130,9 +146,6 @@
   </si>
   <si>
     <t>http://snomed.info/sct</t>
-  </si>
-  <si>
-    <t>2020-09</t>
   </si>
   <si>
     <t>385763009</t>
@@ -278,7 +291,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -405,6 +418,14 @@
         <v>29</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
@@ -412,76 +433,106 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>32</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>34</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F1" t="s" s="1">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G1" t="s" s="1">
-        <v>36</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="C2" t="s" s="2">
-        <v>39</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F2" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="C3" t="s" s="2">
-        <v>39</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E3" t="s" s="2">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="F3" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
